--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCB.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,83 +590,83 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>147</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>42</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>59.5%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>22</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>31.8%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -681,28 +681,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>29.6%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCB_R._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>R. Monteiro</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCB_J._SIBERT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:K5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -717,7 +950,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,7 +973,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: A. Gakou (13 L)</t>
+          <t>Maior volume: A. Gakou (27 L)</t>
         </is>
       </c>
     </row>
@@ -752,7 +985,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: A. Gakou (8 3PA)</t>
+          <t>Maior volume 3pt: A. Gakou (16 3PA)</t>
         </is>
       </c>
     </row>
@@ -764,7 +997,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: A. Gakou (1.4 pts/shot)</t>
+          <t>Mais eficaz: A. Silva (1.5 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -776,7 +1009,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (22 L)</t>
+          <t>Zona mais usada: Restricted Area (42 L)</t>
         </is>
       </c>
     </row>
@@ -788,7 +1021,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (58.3%)</t>
+          <t>Zona mais eficaz: Paint Non-RA (60.0%)</t>
         </is>
       </c>
     </row>
@@ -804,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -937,66 +1170,66 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>59.3%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>8</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>61.5%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1005,52 +1238,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>9</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>33.3%</t>
@@ -1058,238 +1291,238 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
         <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_R._MONTEIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
         <v>9</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
         <v>6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_R._MONTEIRO</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
       </c>
       <c r="R5" t="n">
         <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_M._CORREIA</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Correia</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1297,42 +1530,42 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1340,268 +1573,489 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
         <v>6</v>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_M._CORREIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>M. Correia</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>8</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCB_M._PEIXOTO</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Peixoto</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SCB_M._PEIXOTO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M. Peixoto</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCB_T._SANTOS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T. Santos</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCB_F._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>F. Oliveira</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>11</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1612,10 +2066,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1736,55 +2190,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>61.5%</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1804,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1813,82 +2267,467 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>59.3%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>9</v>
       </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCB_R._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R. Monteiro</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCB_C._CARDOSO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCB_J._SIBERT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCB_A._MOREIRA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Moreira</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCB_V._PANOV</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V. Panov</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S3"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1899,7 +2738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2002,11 +2841,11 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>50.0%</t>
@@ -2014,17 +2853,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2032,18 +2871,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2058,10 +2897,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2074,10 +2913,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
         <v>0.9</v>
@@ -2088,7 +2927,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -2099,56 +2938,56 @@
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_M._CORREIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>M. Correia</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -2161,113 +3000,113 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_M._CORREIA</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Correia</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>60.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2282,63 +3121,63 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>6</v>
       </c>
-      <c r="H7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2350,21 +3189,21 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2372,14 +3211,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2394,75 +3233,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCB_M._PEIXOTO</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Peixoto</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -2470,20 +3319,178 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SCB_T._SANTOS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T. Santos</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCB_M._PEIXOTO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M. Peixoto</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCB_F._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>F. Oliveira</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2494,28 +3501,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>59.3%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCB_J._SIBERT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2590,71 +3780,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2664,95 +3854,95 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="n">
         <v>12</v>
       </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2769,32 +3959,32 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2809,7 +3999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2820,7 +4010,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -2929,49 +4119,49 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2979,27 +4169,27 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3008,217 +4198,217 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_R._MONTEIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_R._MONTEIRO</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_M._CORREIA</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Correia</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3226,88 +4416,98 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -3315,95 +4515,105 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_M._CORREIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>M. Correia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3412,16 +4622,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -3429,73 +4639,253 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>SCB_M._KEGLER</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M. Kegler</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>SCB_M._PEIXOTO</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>M. Peixoto</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCB_T._SANTOS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T. Santos</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCB_F._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>F. Oliveira</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3506,10 +4896,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -3582,46 +4972,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>54.5%</t>
-        </is>
-      </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3641,36 +5031,396 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>29.6%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCB_R._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R. Monteiro</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCB_C._CARDOSO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCB_A._MOREIRA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Moreira</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SCB_V._PANOV</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V. Panov</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="H9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SCB_A._SILVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SCB_J._SIBERT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCB.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,42 +590,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>147</v>
+        <v>224</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -657,16 +657,16 @@
         <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_R._MONTEIRO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -771,29 +771,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -802,12 +802,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCB_R._MONTEIRO</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -816,17 +816,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -861,81 +861,126 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCB_J._SIBERT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -973,7 +1018,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: A. Gakou (27 L)</t>
+          <t>Maior volume: A. Gakou (41 L)</t>
         </is>
       </c>
     </row>
@@ -985,7 +1030,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: A. Gakou (16 3PA)</t>
+          <t>Maior volume 3pt: A. Gakou (21 3PA)</t>
         </is>
       </c>
     </row>
@@ -997,7 +1042,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: A. Silva (1.5 pts/shot)</t>
+          <t>Mais eficaz: M. Correia (1.7 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (42 L)</t>
+          <t>Zona mais usada: Restricted Area (73 L)</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1066,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Paint Non-RA (60.0%)</t>
+          <t>Zona mais eficaz: Corner 3 Left (61.9%)</t>
         </is>
       </c>
     </row>
@@ -1170,66 +1215,66 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>51.2%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>73.3%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>59.3%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>75.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1247,13 +1292,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1261,20 +1306,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1282,11 +1327,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1295,18 +1340,18 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1324,17 +1369,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1347,11 +1392,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1359,11 +1404,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1383,35 +1428,35 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1424,28 +1469,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1453,84 +1498,84 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1540,49 +1585,49 @@
         <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1594,12 +1639,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1607,94 +1652,94 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" t="n">
-        <v>6</v>
-      </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1709,66 +1754,66 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>9</v>
       </c>
-      <c r="D9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>69.2%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="n">
-        <v>14</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1777,215 +1822,229 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCB_M._KEGLER</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Kegler</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
+        <v>17</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>11</v>
-      </c>
-      <c r="S10" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCB_M._PEIXOTO</t>
+          <t>SCB_A._SIBIDE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M. Peixoto</t>
+          <t>A. Sibide</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
       <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCB_T._SANTOS</t>
+          <t>SCB_M._PEIXOTO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T. Santos</t>
+          <t>M. Peixoto</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1994,43 +2053,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCB_F._OLIVEIRA</t>
+          <t>SCB_T._SANTOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F. Oliveira</t>
+          <t>T. Santos</t>
         </is>
       </c>
       <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2038,20 +2101,30 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
         <v>12</v>
-      </c>
-      <c r="S13" t="n">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2066,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2190,42 +2263,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_M._CORREIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>M. Correia</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -2238,12 +2311,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -2251,14 +2324,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -2267,89 +2340,89 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_R._MONTEIRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>78.6%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCB_R._MONTEIRO</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2357,47 +2430,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>19</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -2405,71 +2478,71 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
+        <v>8</v>
+      </c>
+      <c r="S4" t="n">
         <v>3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="E5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" t="n">
+        <v>53</v>
+      </c>
+      <c r="H5" t="n">
+        <v>21</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>51.2%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>15</v>
       </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>14</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -2478,18 +2551,18 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -2498,145 +2571,145 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="E6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
         <v>18</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H6" t="n">
-        <v>12</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>9</v>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2646,7 +2719,7 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2661,46 +2734,46 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>6</v>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2717,17 +2790,171 @@
         </is>
       </c>
       <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SCB_A._MOREIRA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A. Moreira</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="R8" t="n">
-        <v>5</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="G9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
         <v>6</v>
       </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SCB_J._SIBERT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2841,48 +3068,48 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2897,29 +3124,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2927,18 +3154,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2953,11 +3180,11 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
         <v>6</v>
       </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>66.7%</t>
@@ -2965,17 +3192,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2983,18 +3210,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3009,29 +3236,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3050,212 +3277,212 @@
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_R._MONTEIRO</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
         <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_M._KEGLER</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Kegler</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_R._MONTEIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -3263,55 +3490,55 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3319,74 +3546,74 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCB_T._SANTOS</t>
+          <t>SCB_A._SIBIDE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T. Santos</t>
+          <t>A. Sibide</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3401,79 +3628,89 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>11</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCB_F._OLIVEIRA</t>
+          <t>SCB_T._SANTOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F. Oliveira</t>
+          <t>T. Santos</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -3481,13 +3718,15 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>11</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N13"/>
@@ -3604,48 +3843,48 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3660,29 +3899,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3690,18 +3929,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3784,17 +4023,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3802,7 +4041,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -3819,13 +4058,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3837,7 +4076,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3854,17 +4093,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3872,14 +4111,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3889,60 +4128,60 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3955,25 +4194,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3984,7 +4223,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4010,7 +4249,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -4115,28 +4354,28 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>73.3%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4145,31 +4384,31 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3">
@@ -4189,11 +4428,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4202,11 +4441,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4223,7 +4462,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -4231,15 +4470,15 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -4259,11 +4498,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4293,11 +4532,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -4309,36 +4548,36 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -4346,28 +4585,28 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -4379,88 +4618,88 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>17</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>12</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4473,12 +4712,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4486,16 +4725,16 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4503,60 +4742,60 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -4569,27 +4808,27 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -4609,249 +4848,273 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L9" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
         <v>9</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>6</v>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCB_M._KEGLER</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Kegler</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCB_M._PEIXOTO</t>
+          <t>SCB_A._SIBIDE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M. Peixoto</t>
+          <t>A. Sibide</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCB_T._SANTOS</t>
+          <t>SCB_M._PEIXOTO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T. Santos</t>
+          <t>M. Peixoto</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCB_F._OLIVEIRA</t>
+          <t>SCB_T._SANTOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>F. Oliveira</t>
+          <t>T. Santos</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -4859,29 +5122,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -4896,7 +5173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4982,156 +5259,156 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_R._MONTEIRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_R._MONTEIRO</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -5139,52 +5416,52 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -5211,7 +5488,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -5221,15 +5498,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -5256,7 +5533,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -5266,60 +5543,60 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -5332,43 +5609,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -5377,12 +5654,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5391,36 +5668,171 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCB_A._SILVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCB_C._CARDOSO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SCB_M._CORREIA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M. Correia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_SCB.xlsx
@@ -24,11 +24,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,42 +590,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="E2" t="n">
-        <v>224</v>
+        <v>284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,27 +646,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="S2" t="n">
         <v>9</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
         <v>2</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCB_R._MONTEIRO</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -771,25 +771,25 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
         <v>14</v>
       </c>
-      <c r="E2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22</v>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -802,12 +802,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_R._MONTEIRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -816,25 +816,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -857,21 +857,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -879,25 +879,25 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -906,25 +906,25 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -937,12 +937,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -951,36 +951,306 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCB_J._SIBERT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCB_C._CARDOSO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SCB_V._PANOV</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V. Panov</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SCB_C._CARDOSO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SCB_J._SIBERT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCB_C._CARDOSO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -995,7 +1265,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1018,7 +1288,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: A. Gakou (41 L)</t>
+          <t>Maior volume: A. Gakou (49 L)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1300,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: A. Gakou (21 3PA)</t>
+          <t>Maior volume 3pt: A. Gakou (25 3PA)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: M. Correia (1.7 pts/shot)</t>
+          <t>Mais eficaz: M. Correia (1.4 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1324,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (73 L)</t>
+          <t>Zona mais usada: Restricted Area (97 L)</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1336,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Corner 3 Left (61.9%)</t>
+          <t>Zona mais eficaz: Restricted Area (61.9%)</t>
         </is>
       </c>
     </row>
@@ -1215,30 +1485,30 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1250,11 +1520,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1263,18 +1533,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1292,34 +1562,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1327,11 +1597,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1340,18 +1610,18 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1369,34 +1639,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1404,11 +1674,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1417,136 +1687,136 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1554,28 +1824,28 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>7</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1585,7 +1855,7 @@
         <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1600,34 +1870,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" t="n">
+        <v>27</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>8</v>
       </c>
-      <c r="E7" t="n">
-        <v>18</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>7</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1635,11 +1905,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1659,56 +1929,56 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_M._CORREIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>M. Correia</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
+        <v>27</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>13</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1716,55 +1986,55 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCB_M._CORREIA</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Correia</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1772,16 +2042,16 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1789,93 +2059,93 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>3</v>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
         <v>13</v>
       </c>
-      <c r="D10" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>17</v>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>5</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1883,17 +2153,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1908,17 +2178,17 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1931,11 +2201,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1943,11 +2213,11 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1967,7 +2237,7 @@
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2121,7 +2391,7 @@
         <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>12</v>
@@ -2272,33 +2542,33 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" t="n">
         <v>13</v>
       </c>
-      <c r="F2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" t="n">
-        <v>22</v>
-      </c>
-      <c r="H2" t="n">
-        <v>9</v>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -2307,11 +2577,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2320,18 +2590,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -2340,12 +2610,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCB_R._MONTEIRO</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2353,76 +2623,76 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>19.0%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>14</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>78.6%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2430,62 +2700,62 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>55.1%</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>49</v>
+      </c>
+      <c r="F4" t="n">
+        <v>27</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>44.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>51.0%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>73.7%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>53.8%</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -2494,89 +2764,89 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="n">
         <v>22</v>
       </c>
-      <c r="G5" t="n">
-        <v>53</v>
-      </c>
       <c r="H5" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>15</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>73.3%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_M._KEGLER</t>
+          <t>SCB_R._MONTEIRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Kegler</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2584,29 +2854,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2615,45 +2885,45 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>18</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>6</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2661,55 +2931,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>11</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2719,95 +2989,95 @@
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>13</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="O8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>4</v>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2815,76 +3085,76 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2892,65 +3162,65 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
-        <v>20</v>
-      </c>
-      <c r="H10" t="n">
-        <v>15</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>62.5%</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>11</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3068,26 +3338,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -3098,11 +3368,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -3124,29 +3394,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3154,18 +3424,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3180,29 +3450,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3210,11 +3480,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -3227,169 +3497,169 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_M._KEGLER</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Kegler</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I6" t="n">
         <v>1.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -3404,26 +3674,26 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I8" t="n">
         <v>1.1</v>
@@ -3434,18 +3704,18 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3460,29 +3730,29 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -3490,18 +3760,18 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -3516,29 +3786,29 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
         <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3546,15 +3816,15 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
@@ -3584,29 +3854,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>4</v>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -3740,10 +4010,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -3834,117 +4104,229 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_M._CORREIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>M. Correia</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>44.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>51.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>49</v>
+      </c>
+      <c r="H3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>73.7%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>SCB_J._SIBERT</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>J. Sibert</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCB_C._CARDOSO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>4</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>24</v>
-      </c>
-      <c r="H3" t="n">
-        <v>20</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>11</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="N5" t="n">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4023,17 +4405,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4041,14 +4423,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -4058,17 +4440,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4076,7 +4458,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -4093,25 +4475,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -4128,32 +4510,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4163,25 +4545,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -4198,25 +4580,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -4249,7 +4631,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -4358,11 +4740,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4371,11 +4753,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4392,19 +4774,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4428,11 +4810,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4441,11 +4823,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4454,31 +4836,31 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -4498,11 +4880,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4511,156 +4893,156 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>26</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>19</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>47.4%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -4668,23 +5050,23 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>22</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>17</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>47.1%</t>
-        </is>
-      </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -4708,11 +5090,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4742,39 +5124,39 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_M._CORREIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>M. Correia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -4782,64 +5164,64 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCB_M._CORREIA</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Correia</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4848,45 +5230,45 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>18</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>13</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>61.5%</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -4894,40 +5276,40 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4935,7 +5317,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4948,27 +5330,27 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
@@ -4988,11 +5370,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5008,15 +5390,25 @@
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -5028,7 +5420,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="12">
@@ -5173,7 +5565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5263,17 +5655,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -5281,7 +5673,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -5308,17 +5700,17 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3" t="n">
         <v>14</v>
       </c>
-      <c r="E3" t="n">
-        <v>11</v>
-      </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -5326,7 +5718,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -5339,12 +5731,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5353,29 +5745,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -5384,12 +5776,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5398,29 +5790,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
@@ -5443,25 +5835,25 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -5474,12 +5866,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5488,7 +5880,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -5498,19 +5890,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -5519,84 +5911,84 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -5609,43 +6001,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -5654,12 +6046,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCB_M._KEGLER</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M. Kegler</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5668,43 +6060,43 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
         <v>6</v>
       </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5713,43 +6105,43 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5758,29 +6150,29 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
@@ -5789,50 +6181,275 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>SCB_M._CORREIA</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>M. Correia</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SCB_R._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>R. Monteiro</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SCB_A._SILVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
-        <v>6</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SCB_A._SIBIDE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A. Sibide</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
+      <c r="H18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>